--- a/generated/sources/reports/retail_controlling/weekly_flash/Flash_W42_2026.xlsx
+++ b/generated/sources/reports/retail_controlling/weekly_flash/Flash_W42_2026.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="211">
   <si>
-    <t>MONCLER  |  Retail Controlling</t>
+    <t>VALENTINO  |  Retail Controlling</t>
   </si>
   <si>
     <t>WEEKLY SALES FLASH - WEEK 42 / 2026</t>
@@ -64,13 +64,13 @@
     <t>- Japan: clients buying ahead of 01/11 price increase (announced 09/10).</t>
   </si>
   <si>
-    <t>- SEL01: ILVARO replenishment released by Incheon customs 13/10 (planned 08/10).</t>
+    <t>- SEL01: IRIDIA replenishment released by Incheon customs 13/10 (planned 08/10).</t>
   </si>
   <si>
     <t>- Competitor pop-up opened in front of SEL01 on 15/10.</t>
   </si>
   <si>
-    <t>- MAIRE black: DC re-supply received 16/10, store allocations shipping this week.</t>
+    <t>- AUREA black: DC re-supply received 16/10, store allocations shipping this week.</t>
   </si>
   <si>
     <t>Confidential - Internal use only. Source: SAP BW / POS (Xstore), store door counters. Retail Controlling.</t>
@@ -592,55 +592,55 @@
     <t>Units returned</t>
   </si>
   <si>
-    <t>MAYA</t>
+    <t>NOVA</t>
   </si>
   <si>
     <t>Outerwear</t>
   </si>
   <si>
-    <t>MAIRE</t>
-  </si>
-  <si>
-    <t>HERMINE</t>
-  </si>
-  <si>
-    <t>BADY</t>
-  </si>
-  <si>
-    <t>MONTGENEVRE</t>
-  </si>
-  <si>
-    <t>ILVARO</t>
-  </si>
-  <si>
-    <t>MONTCLA</t>
-  </si>
-  <si>
-    <t>KARAKORUM</t>
-  </si>
-  <si>
-    <t>FLAMMETTE</t>
-  </si>
-  <si>
-    <t>TRICOT PADDED CARDIGAN</t>
+    <t>AUREA</t>
+  </si>
+  <si>
+    <t>LIVIANA</t>
+  </si>
+  <si>
+    <t>ARIA</t>
+  </si>
+  <si>
+    <t>MONTELUCE</t>
+  </si>
+  <si>
+    <t>IRIDIA</t>
+  </si>
+  <si>
+    <t>MISTRAL</t>
+  </si>
+  <si>
+    <t>COSIMO</t>
+  </si>
+  <si>
+    <t>FIAMMETTA</t>
+  </si>
+  <si>
+    <t>VLOGO PADDED CARDIGAN</t>
   </si>
   <si>
     <t>Knitwear</t>
   </si>
   <si>
-    <t>AMBRINE</t>
-  </si>
-  <si>
-    <t>ARNEB</t>
-  </si>
-  <si>
-    <t>ROSIERE</t>
-  </si>
-  <si>
-    <t>LOGO CARDIGAN</t>
-  </si>
-  <si>
-    <t>LOGO HOODIE</t>
+    <t>AMALIA</t>
+  </si>
+  <si>
+    <t>ARTEM</t>
+  </si>
+  <si>
+    <t>RIVIERA</t>
+  </si>
+  <si>
+    <t>VLOGO CARDIGAN</t>
+  </si>
+  <si>
+    <t>VLOGO HOODIE</t>
   </si>
   <si>
     <t>Jersey</t>
